--- a/event_registration_forms/016_event_ticketing_subscription_form--event_registration_forms.xlsx
+++ b/event_registration_forms/016_event_ticketing_subscription_form--event_registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -592,12 +592,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -625,12 +625,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'payment_gateway',_'label':_'payment_gateway',_'type':_'select_one',_'options':_[{'id':_1,_'name':_'payment_gateway',_'label':_'payment_gateway'},_{'id':_2,_'name':_'email_gateway',_'label':_'email_gateway'},_{'id':_3,_'name':_'other_gateway',_'label':_'other'}]}</t>
+          <t>payment_gateway</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'payment_gateway', 'label': 'Payment Gateway', 'type': 'select_one', 'options': [{'id': 1, 'name': 'payment_gateway', 'label': 'Payment Gateway'}, {'id': 2, 'name': 'email_gateway', 'label': 'Email Gateway'}, {'id': 3, 'name': 'other_gateway', 'label': 'Other'}]}</t>
+          <t>Payment Gateway</t>
         </is>
       </c>
     </row>
@@ -642,12 +642,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'payment_method',_'label':_'payment_method',_'type':_'select_one',_'options':_[{'id':_1,_'name':_'card',_'label':_'card'},_{'id':_2,_'name':_'bank',_'label':_'bank'},_{'id':_3,_'name':_'cash',_'label':_'cash'}]}</t>
+          <t>payment_method</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'payment_method', 'label': 'Payment Method', 'type': 'select_one', 'options': [{'id': 1, 'name': 'card', 'label': 'Card'}, {'id': 2, 'name': 'bank', 'label': 'Bank'}, {'id': 3, 'name': 'cash', 'label': 'Cash'}]}</t>
+          <t>Payment Method</t>
         </is>
       </c>
     </row>
@@ -659,12 +659,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'event_info',_'label':_'event_info',_'type':_'object',_'options':_[]}</t>
+          <t>event_info</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'event_info', 'label': 'Event Info', 'type': 'object', 'options': []}</t>
+          <t>Event Info</t>
         </is>
       </c>
     </row>
@@ -676,12 +676,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'time',_'label':_'time',_'type':_'time',_'options':_[]}</t>
+          <t>time</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'time', 'label': 'Time', 'type': 'time', 'options': []}</t>
+          <t>Time</t>
         </is>
       </c>
     </row>
@@ -693,12 +693,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'date',_'label':_'date',_'type':_'date',_'options':_[]}</t>
+          <t>date</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'date', 'label': 'Date', 'type': 'date', 'options': []}</t>
+          <t>Date</t>
         </is>
       </c>
     </row>
@@ -710,12 +710,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_6,_'name':_'event_date',_'label':_'event_date',_'type':_'date',_'options':_[]}</t>
+          <t>event_date</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 6, 'name': 'event_date', 'label': 'Event Date', 'type': 'date', 'options': []}</t>
+          <t>Event Date</t>
         </is>
       </c>
     </row>
@@ -727,12 +727,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_7,_'name':_'time_in',_'label':_'time_in',_'type':_'time',_'options':_[]}</t>
+          <t>time_in</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 7, 'name': 'time_in', 'label': 'Time In', 'type': 'time', 'options': []}</t>
+          <t>Time In</t>
         </is>
       </c>
     </row>
@@ -744,12 +744,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_8,_'name':_'time_out',_'label':_'time_out',_'type':_'time',_'options':_[]}</t>
+          <t>time_out</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 8, 'name': 'time_out', 'label': 'Time Out', 'type': 'time', 'options': []}</t>
+          <t>Time Out</t>
         </is>
       </c>
     </row>
@@ -761,12 +761,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_9,_'name':_'time_zone',_'label':_'time_zone',_'type':_'select_one',_'options':_[{'id':_1,_'name':_'america_los_angeles',_'label':_'america/los_angeles'},_{'id':_2,_'name':_'asia_tokyo',_'label':_'asia/tokyo'},_{'id':_3,_'name':_'europe_london',_'label':_'europe/london'}]}</t>
+          <t>time_zone</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 9, 'name': 'time_zone', 'label': 'Time Zone', 'type': 'select_one', 'options': [{'id': 1, 'name': 'america_los_angeles', 'label': 'America/Los Angeles'}, {'id': 2, 'name': 'asia_tokyo', 'label': 'Asia/Tokyo'}, {'id': 3, 'name': 'europe_london', 'label': 'Europe/London'}]}</t>
+          <t>Time Zone</t>
         </is>
       </c>
     </row>
@@ -778,12 +778,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_10,_'name':_'timezone',_'label':_'timezone',_'type':_'select_one',_'options':_[{'id':_1,_'name':_'america_los_angeles',_'label':_'america/los_angeles',_'type':_'select_one',_'options':_[{'id':_1,_'name':_'los_angeles',_'label':_'los_angeles'},_{'id':_2,_'name':_'new_york',_'label':_'new_york'}]},_{'id':_2,_'name':_'asia_tokyo',_'label':_'asia/tokyo',_'type':_'select_one',_'options':_[{'id':_1,_'name':_'tokyo',_'label':_'tokyo'},_{'id':_2,_'name':_'seoul',_'label':_'seoul'}]},_{'id':_3,_'name':_'europe_london',_'label':_'europe/london',_'type':_'select_one',_'options':_[{'id':_1,_'name':_'london',_'label':_'london'},_{'id':_2,_'name':_'paris',_'label':_'paris'}]}]}</t>
+          <t>timezone</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 10, 'name': 'timezone', 'label': 'Timezone', 'type': 'select_one', 'options': [{'id': 1, 'name': 'america_los_angeles', 'label': 'America/Los Angeles', 'type': 'select_one', 'options': [{'id': 1, 'name': 'los_angeles', 'label': 'Los Angeles'}, {'id': 2, 'name': 'new_york', 'label': 'New York'}]}, {'id': 2, 'name': 'asia_tokyo', 'label': 'Asia/Tokyo', 'type': 'select_one', 'options': [{'id': 1, 'name': 'tokyo', 'label': 'Tokyo'}, {'id': 2, 'name': 'seoul', 'label': 'Seoul'}]}, {'id': 3, 'name': 'europe_london', 'label': 'Europe/London', 'type': 'select_one', 'options': [{'id': 1, 'name': 'london', 'label': 'London'}, {'id': 2, 'name': 'paris', 'label': 'Paris'}]}]}</t>
+          <t>Timezone</t>
         </is>
       </c>
     </row>
@@ -795,12 +795,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_11,_'name':_'payment_method',_'label':_'payment_method',_'type':_'select_one',_'options':_[{'id':_1,_'name':_'card',_'label':_'card'},_{'id':_2,_'name':_'bank',_'label':_'bank'},_{'id':_3,_'name':_'cash',_'label':_'cash'}]}</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 11, 'name': 'payment_method', 'label': 'Payment Method', 'type': 'select_one', 'options': [{'id': 1, 'name': 'card', 'label': 'Card'}, {'id': 2, 'name': 'bank', 'label': 'Bank'}, {'id': 3, 'name': 'cash', 'label': 'Cash'}]}</t>
+          <t>Currency</t>
         </is>
       </c>
     </row>
@@ -812,12 +812,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_12,_'name':_'currency',_'label':_'currency',_'type':_'select_one',_'options':_[{'id':_1,_'name':_'usd',_'label':_'usd'},_{'id':_2,_'name':_'eur',_'label':_'eur'},_{'id':_3,_'name':_'jpy',_'label':_'jpy'}]}</t>
+          <t>amount</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 12, 'name': 'currency', 'label': 'Currency', 'type': 'select_one', 'options': [{'id': 1, 'name': 'usd', 'label': 'USD'}, {'id': 2, 'name': 'eur', 'label': 'EUR'}, {'id': 3, 'name': 'jpy', 'label': 'JPY'}]}</t>
+          <t>Amount</t>
         </is>
       </c>
     </row>
@@ -829,12 +829,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_13,_'name':_'amount',_'label':_'amount',_'type':_'integer',_'options':_[]}</t>
+          <t>discount</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 13, 'name': 'amount', 'label': 'Amount', 'type': 'integer', 'options': []}</t>
+          <t>Discount</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_14,_'name':_'discount',_'label':_'discount',_'type':_'integer',_'options':_[]}</t>
+          <t>event_type</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 14, 'name': 'discount', 'label': 'Discount', 'type': 'integer', 'options': []}</t>
+          <t>Event Type</t>
         </is>
       </c>
     </row>
@@ -863,29 +863,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_15,_'name':_'event_type',_'label':_'event_type',_'type':_'select_one',_'options':_[{'id':_1,_'name':_'in_person',_'label':_'in_person'},_{'id':_2,_'name':_'online',_'label':_'online'},_{'id':_3,_'name':_'offline',_'label':_'offline'}]}</t>
+          <t>location</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 15, 'name': 'event_type', 'label': 'Event Type', 'type': 'select_one', 'options': [{'id': 1, 'name': 'in_person', 'label': 'In Person'}, {'id': 2, 'name': 'online', 'label': 'Online'}, {'id': 3, 'name': 'offline', 'label': 'Offline'}]}</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>event_ticketing_form_input_fields_choices</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>{'id':_16,_'name':_'location',_'label':_'location',_'type':_'select_one',_'options':_[{'id':_1,_'name':_'event_ticketing_form_location',_'label':_'event_location'},_{'id':_2,_'name':_'event_ticketing_form_location_2',_'label':_'location_2'},_{'id':_3,_'name':_'event_ticketing_form_location_3',_'label':_'event_location_3'}]}</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>{'id': 16, 'name': 'location', 'label': 'Location', 'type': 'select_one', 'options': [{'id': 1, 'name': 'event_ticketing_form_location', 'label': 'Event Location'}, {'id': 2, 'name': 'event_ticketing_form_location_2', 'label': 'Location 2'}, {'id': 3, 'name': 'event_ticketing_form_location_3', 'label': 'Event Location 3'}]}</t>
+          <t>Location</t>
         </is>
       </c>
     </row>
